--- a/artfynd/A 48337-2021 artfynd.xlsx
+++ b/artfynd/A 48337-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48337-2021 artfynd.xlsx
+++ b/artfynd/A 48337-2021 artfynd.xlsx
@@ -2391,10 +2391,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121066911</v>
+        <v>121066920</v>
       </c>
       <c r="B18" t="n">
-        <v>90652</v>
+        <v>78680</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2403,25 +2403,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>864</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>607566</v>
+        <v>607402</v>
       </c>
       <c r="R18" t="n">
-        <v>7222773</v>
+        <v>7222693</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2497,10 +2497,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121066920</v>
+        <v>121066911</v>
       </c>
       <c r="B19" t="n">
-        <v>78680</v>
+        <v>90652</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2509,25 +2509,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>864</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>607402</v>
+        <v>607566</v>
       </c>
       <c r="R19" t="n">
-        <v>7222693</v>
+        <v>7222773</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 48337-2021 artfynd.xlsx
+++ b/artfynd/A 48337-2021 artfynd.xlsx
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121066923</v>
+        <v>121066920</v>
       </c>
       <c r="B4" t="n">
-        <v>82382</v>
+        <v>78683</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607377</v>
+        <v>607402</v>
       </c>
       <c r="R4" t="n">
-        <v>7222687</v>
+        <v>7222693</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121066915</v>
+        <v>121066910</v>
       </c>
       <c r="B5" t="n">
-        <v>79679</v>
+        <v>79711</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,25 +1025,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>607550</v>
+        <v>607702</v>
       </c>
       <c r="R5" t="n">
-        <v>7222762</v>
+        <v>7222817</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121066916</v>
+        <v>121066925</v>
       </c>
       <c r="B6" t="n">
-        <v>98092</v>
+        <v>79717</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1159,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>607498</v>
+        <v>607361</v>
       </c>
       <c r="R6" t="n">
-        <v>7222743</v>
+        <v>7222693</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121066913</v>
+        <v>121066924</v>
       </c>
       <c r="B7" t="n">
-        <v>82382</v>
+        <v>78601</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,21 +1241,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1265,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>607553</v>
+        <v>607366</v>
       </c>
       <c r="R7" t="n">
-        <v>7222773</v>
+        <v>7222690</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121066910</v>
+        <v>121066919</v>
       </c>
       <c r="B8" t="n">
-        <v>79708</v>
+        <v>97035</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,21 +1347,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>607702</v>
+        <v>607427</v>
       </c>
       <c r="R8" t="n">
-        <v>7222817</v>
+        <v>7222722</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,10 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121066919</v>
+        <v>121066911</v>
       </c>
       <c r="B9" t="n">
-        <v>97025</v>
+        <v>90662</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1453,21 +1453,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>607427</v>
+        <v>607566</v>
       </c>
       <c r="R9" t="n">
-        <v>7222722</v>
+        <v>7222773</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1543,10 +1543,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121066922</v>
+        <v>121066921</v>
       </c>
       <c r="B10" t="n">
-        <v>82382</v>
+        <v>79710</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1555,25 +1555,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>6461</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>607379</v>
+        <v>607386</v>
       </c>
       <c r="R10" t="n">
-        <v>7222687</v>
+        <v>7222698</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1652,7 +1652,7 @@
         <v>121066914</v>
       </c>
       <c r="B11" t="n">
-        <v>79708</v>
+        <v>79711</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1755,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121066918</v>
+        <v>121066913</v>
       </c>
       <c r="B12" t="n">
-        <v>74705</v>
+        <v>82385</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1771,21 +1771,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>607441</v>
+        <v>607553</v>
       </c>
       <c r="R12" t="n">
-        <v>7222739</v>
+        <v>7222773</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1861,10 +1861,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121066912</v>
+        <v>121066923</v>
       </c>
       <c r="B13" t="n">
-        <v>74705</v>
+        <v>82385</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1877,21 +1877,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>607556</v>
+        <v>607377</v>
       </c>
       <c r="R13" t="n">
-        <v>7222767</v>
+        <v>7222687</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1967,10 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121066921</v>
+        <v>121066916</v>
       </c>
       <c r="B14" t="n">
-        <v>79707</v>
+        <v>98102</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1983,21 +1983,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6461</v>
+        <v>221952</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>607386</v>
+        <v>607498</v>
       </c>
       <c r="R14" t="n">
-        <v>7222698</v>
+        <v>7222743</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121066917</v>
+        <v>121066912</v>
       </c>
       <c r="B15" t="n">
-        <v>78598</v>
+        <v>74708</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2089,21 +2089,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>607474</v>
+        <v>607556</v>
       </c>
       <c r="R15" t="n">
-        <v>7222766</v>
+        <v>7222767</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2179,10 +2179,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121066924</v>
+        <v>121066918</v>
       </c>
       <c r="B16" t="n">
-        <v>78598</v>
+        <v>74708</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2195,21 +2195,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>607366</v>
+        <v>607441</v>
       </c>
       <c r="R16" t="n">
-        <v>7222690</v>
+        <v>7222739</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2285,10 +2285,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121066925</v>
+        <v>121066915</v>
       </c>
       <c r="B17" t="n">
-        <v>79714</v>
+        <v>79682</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2297,25 +2297,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>607361</v>
+        <v>607550</v>
       </c>
       <c r="R17" t="n">
-        <v>7222693</v>
+        <v>7222762</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2391,10 +2391,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121066920</v>
+        <v>121066917</v>
       </c>
       <c r="B18" t="n">
-        <v>78680</v>
+        <v>78601</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2407,21 +2407,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>607402</v>
+        <v>607474</v>
       </c>
       <c r="R18" t="n">
-        <v>7222693</v>
+        <v>7222766</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2497,10 +2497,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121066911</v>
+        <v>121066922</v>
       </c>
       <c r="B19" t="n">
-        <v>90652</v>
+        <v>82385</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2509,25 +2509,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>607566</v>
+        <v>607379</v>
       </c>
       <c r="R19" t="n">
-        <v>7222773</v>
+        <v>7222687</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 48337-2021 artfynd.xlsx
+++ b/artfynd/A 48337-2021 artfynd.xlsx
@@ -1861,10 +1861,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121066923</v>
+        <v>121066916</v>
       </c>
       <c r="B13" t="n">
-        <v>82385</v>
+        <v>98102</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1873,25 +1873,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>607377</v>
+        <v>607498</v>
       </c>
       <c r="R13" t="n">
-        <v>7222687</v>
+        <v>7222743</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1967,10 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121066916</v>
+        <v>121066923</v>
       </c>
       <c r="B14" t="n">
-        <v>98102</v>
+        <v>82385</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1979,25 +1979,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221952</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>607498</v>
+        <v>607377</v>
       </c>
       <c r="R14" t="n">
-        <v>7222743</v>
+        <v>7222687</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 48337-2021 artfynd.xlsx
+++ b/artfynd/A 48337-2021 artfynd.xlsx
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121066910</v>
+        <v>121066918</v>
       </c>
       <c r="B5" t="n">
-        <v>79711</v>
+        <v>74708</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,25 +1025,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>607702</v>
+        <v>607441</v>
       </c>
       <c r="R5" t="n">
-        <v>7222817</v>
+        <v>7222739</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121066925</v>
+        <v>121066917</v>
       </c>
       <c r="B6" t="n">
-        <v>79717</v>
+        <v>78601</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,20 +1131,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1159,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>607361</v>
+        <v>607474</v>
       </c>
       <c r="R6" t="n">
-        <v>7222693</v>
+        <v>7222766</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121066924</v>
+        <v>121066921</v>
       </c>
       <c r="B7" t="n">
-        <v>78601</v>
+        <v>79710</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,25 +1237,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1265,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>607366</v>
+        <v>607386</v>
       </c>
       <c r="R7" t="n">
-        <v>7222690</v>
+        <v>7222698</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121066919</v>
+        <v>121066914</v>
       </c>
       <c r="B8" t="n">
-        <v>97035</v>
+        <v>79711</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,21 +1347,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>607427</v>
+        <v>607549</v>
       </c>
       <c r="R8" t="n">
-        <v>7222722</v>
+        <v>7222768</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,10 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121066911</v>
+        <v>121066910</v>
       </c>
       <c r="B9" t="n">
-        <v>90662</v>
+        <v>79711</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1453,21 +1453,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>607566</v>
+        <v>607702</v>
       </c>
       <c r="R9" t="n">
-        <v>7222773</v>
+        <v>7222817</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1543,10 +1543,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121066921</v>
+        <v>121066925</v>
       </c>
       <c r="B10" t="n">
-        <v>79710</v>
+        <v>79717</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6461</v>
+        <v>6463</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>607386</v>
+        <v>607361</v>
       </c>
       <c r="R10" t="n">
-        <v>7222698</v>
+        <v>7222693</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1649,10 +1649,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121066914</v>
+        <v>121066923</v>
       </c>
       <c r="B11" t="n">
-        <v>79711</v>
+        <v>82385</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1661,25 +1661,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>607549</v>
+        <v>607377</v>
       </c>
       <c r="R11" t="n">
-        <v>7222768</v>
+        <v>7222687</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1755,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121066913</v>
+        <v>121066916</v>
       </c>
       <c r="B12" t="n">
-        <v>82385</v>
+        <v>98102</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1767,25 +1767,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>607553</v>
+        <v>607498</v>
       </c>
       <c r="R12" t="n">
-        <v>7222773</v>
+        <v>7222743</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1861,10 +1861,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121066916</v>
+        <v>121066924</v>
       </c>
       <c r="B13" t="n">
-        <v>98102</v>
+        <v>78601</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1873,25 +1873,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>607498</v>
+        <v>607366</v>
       </c>
       <c r="R13" t="n">
-        <v>7222743</v>
+        <v>7222690</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1967,10 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121066923</v>
+        <v>121066919</v>
       </c>
       <c r="B14" t="n">
-        <v>82385</v>
+        <v>97035</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1979,25 +1979,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>607377</v>
+        <v>607427</v>
       </c>
       <c r="R14" t="n">
-        <v>7222687</v>
+        <v>7222722</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121066912</v>
+        <v>121066911</v>
       </c>
       <c r="B15" t="n">
-        <v>74708</v>
+        <v>90662</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2085,25 +2085,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>607556</v>
+        <v>607566</v>
       </c>
       <c r="R15" t="n">
-        <v>7222767</v>
+        <v>7222773</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2179,10 +2179,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121066918</v>
+        <v>121066922</v>
       </c>
       <c r="B16" t="n">
-        <v>74708</v>
+        <v>82385</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2195,21 +2195,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>607441</v>
+        <v>607379</v>
       </c>
       <c r="R16" t="n">
-        <v>7222739</v>
+        <v>7222687</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2391,10 +2391,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121066917</v>
+        <v>121066912</v>
       </c>
       <c r="B18" t="n">
-        <v>78601</v>
+        <v>74708</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2407,21 +2407,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>607474</v>
+        <v>607556</v>
       </c>
       <c r="R18" t="n">
-        <v>7222766</v>
+        <v>7222767</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2497,7 +2497,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121066922</v>
+        <v>121066913</v>
       </c>
       <c r="B19" t="n">
         <v>82385</v>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>607379</v>
+        <v>607553</v>
       </c>
       <c r="R19" t="n">
-        <v>7222687</v>
+        <v>7222773</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 48337-2021 artfynd.xlsx
+++ b/artfynd/A 48337-2021 artfynd.xlsx
@@ -1861,10 +1861,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121066924</v>
+        <v>121066919</v>
       </c>
       <c r="B13" t="n">
-        <v>78601</v>
+        <v>97035</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1873,25 +1873,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>607366</v>
+        <v>607427</v>
       </c>
       <c r="R13" t="n">
-        <v>7222690</v>
+        <v>7222722</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1967,10 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121066919</v>
+        <v>121066924</v>
       </c>
       <c r="B14" t="n">
-        <v>97035</v>
+        <v>78601</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1979,25 +1979,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>607427</v>
+        <v>607366</v>
       </c>
       <c r="R14" t="n">
-        <v>7222722</v>
+        <v>7222690</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 48337-2021 artfynd.xlsx
+++ b/artfynd/A 48337-2021 artfynd.xlsx
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121066920</v>
+        <v>121066921</v>
       </c>
       <c r="B4" t="n">
-        <v>78683</v>
+        <v>79713</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,25 +919,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>864</v>
+        <v>6461</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607402</v>
+        <v>607386</v>
       </c>
       <c r="R4" t="n">
-        <v>7222693</v>
+        <v>7222698</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121066918</v>
+        <v>121066916</v>
       </c>
       <c r="B5" t="n">
-        <v>74708</v>
+        <v>98115</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,25 +1025,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>221952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>607441</v>
+        <v>607498</v>
       </c>
       <c r="R5" t="n">
-        <v>7222739</v>
+        <v>7222743</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121066917</v>
+        <v>121066913</v>
       </c>
       <c r="B6" t="n">
-        <v>78601</v>
+        <v>82388</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1159,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>607474</v>
+        <v>607553</v>
       </c>
       <c r="R6" t="n">
-        <v>7222766</v>
+        <v>7222773</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121066921</v>
+        <v>121066922</v>
       </c>
       <c r="B7" t="n">
-        <v>79710</v>
+        <v>82388</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,25 +1237,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6461</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1265,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>607386</v>
+        <v>607379</v>
       </c>
       <c r="R7" t="n">
-        <v>7222698</v>
+        <v>7222687</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121066914</v>
+        <v>121066923</v>
       </c>
       <c r="B8" t="n">
-        <v>79711</v>
+        <v>82388</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,25 +1343,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>607549</v>
+        <v>607377</v>
       </c>
       <c r="R8" t="n">
-        <v>7222768</v>
+        <v>7222687</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,10 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121066910</v>
+        <v>121066924</v>
       </c>
       <c r="B9" t="n">
-        <v>79711</v>
+        <v>78604</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,25 +1449,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>607702</v>
+        <v>607366</v>
       </c>
       <c r="R9" t="n">
-        <v>7222817</v>
+        <v>7222690</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,7 +1546,7 @@
         <v>121066925</v>
       </c>
       <c r="B10" t="n">
-        <v>79717</v>
+        <v>79720</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1649,10 +1649,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121066923</v>
+        <v>121066911</v>
       </c>
       <c r="B11" t="n">
-        <v>82385</v>
+        <v>90674</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1661,25 +1661,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>607377</v>
+        <v>607566</v>
       </c>
       <c r="R11" t="n">
-        <v>7222687</v>
+        <v>7222773</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1755,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121066916</v>
+        <v>121066920</v>
       </c>
       <c r="B12" t="n">
-        <v>98102</v>
+        <v>78686</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1767,25 +1767,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>864</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>607498</v>
+        <v>607402</v>
       </c>
       <c r="R12" t="n">
-        <v>7222743</v>
+        <v>7222693</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1861,10 +1861,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121066919</v>
+        <v>121066910</v>
       </c>
       <c r="B13" t="n">
-        <v>97035</v>
+        <v>79714</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1877,21 +1877,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>607427</v>
+        <v>607702</v>
       </c>
       <c r="R13" t="n">
-        <v>7222722</v>
+        <v>7222817</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1967,10 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121066924</v>
+        <v>121066912</v>
       </c>
       <c r="B14" t="n">
-        <v>78601</v>
+        <v>74710</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1983,21 +1983,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>607366</v>
+        <v>607556</v>
       </c>
       <c r="R14" t="n">
-        <v>7222690</v>
+        <v>7222767</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121066911</v>
+        <v>121066915</v>
       </c>
       <c r="B15" t="n">
-        <v>90662</v>
+        <v>79685</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2085,25 +2085,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>607566</v>
+        <v>607550</v>
       </c>
       <c r="R15" t="n">
-        <v>7222773</v>
+        <v>7222762</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2179,10 +2179,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121066922</v>
+        <v>121066919</v>
       </c>
       <c r="B16" t="n">
-        <v>82385</v>
+        <v>97048</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2191,25 +2191,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>607379</v>
+        <v>607427</v>
       </c>
       <c r="R16" t="n">
-        <v>7222687</v>
+        <v>7222722</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2285,10 +2285,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121066915</v>
+        <v>121066914</v>
       </c>
       <c r="B17" t="n">
-        <v>79682</v>
+        <v>79714</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2297,25 +2297,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>607550</v>
+        <v>607549</v>
       </c>
       <c r="R17" t="n">
-        <v>7222762</v>
+        <v>7222768</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2391,10 +2391,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121066912</v>
+        <v>121066918</v>
       </c>
       <c r="B18" t="n">
-        <v>74708</v>
+        <v>74710</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>607556</v>
+        <v>607441</v>
       </c>
       <c r="R18" t="n">
-        <v>7222767</v>
+        <v>7222739</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2497,10 +2497,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121066913</v>
+        <v>121066917</v>
       </c>
       <c r="B19" t="n">
-        <v>82385</v>
+        <v>78604</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2513,21 +2513,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>607553</v>
+        <v>607474</v>
       </c>
       <c r="R19" t="n">
-        <v>7222773</v>
+        <v>7222766</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
